--- a/data/trans_orig/IP26D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP26D_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7801</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4137</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12512</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5674</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2704</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11035</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10518</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,58%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7801</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4120</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12791</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>32500</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25205</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40195</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>48,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>31271</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24657</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38613</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24455</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>38737</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,27%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>32500</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>26038</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>39824</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>38,96%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53663</t>
+          <t>54379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74381</t>
+          <t>74185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>43121</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>35418</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50394</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>51,69%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>42,46%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>60,41%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>49269</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>42356</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>56551</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>42302</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>56562</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>57,15%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>49,13%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>65,59%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>43121</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>35172</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>50190</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>51,69%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80745</t>
+          <t>82160</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>103071</t>
+          <t>102556</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>83422</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>83422</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>83422</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>86214</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>86214</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>86214</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>83422</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>83422</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>83422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22276</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15249</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>30381</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>15413</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10541</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>23219</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>22231</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>3,82%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>22276</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>15738</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>30271</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29037</t>
+          <t>29099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47530</t>
+          <t>47860</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>185042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>168573</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>200712</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>39,83%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>36,29%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>43,21%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>153485</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>136941</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>169106</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>137347</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>167656</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>38,02%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>33,92%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>41,89%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>185042</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>168702</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>201768</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>39,83%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>314902</t>
+          <t>315165</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>361942</t>
+          <t>362113</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,71%</t>
         </is>
       </c>
     </row>
@@ -1405,72 +1405,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>257207</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>241906</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>275864</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>59,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>355</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>234783</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>218419</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>250605</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>220377</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>251813</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>58,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,08%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>257207</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>240198</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>274071</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>55,37%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>470068</t>
+          <t>471410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>516286</t>
+          <t>518110</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,68%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>464526</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>464526</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>464526</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>610</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>403681</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>403681</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>403681</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>464526</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>464526</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>464526</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1635,72 +1635,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4514</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>2647</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6191</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6535</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1279</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3898</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51281</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41064</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>60140</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,98%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>39,51%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>61143</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>50846</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>71847</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>50800</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>71033</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>36,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>30,31%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>51281</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>42042</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>61033</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>33,69%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98705</t>
+          <t>99121</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126907</t>
+          <t>127593</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>99648</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90768</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>109818</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>65,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>59,63%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>103940</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>92852</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>114058</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>94110</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>113664</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>61,97%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>55,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>99648</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>89933</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>109637</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>65,47%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>189318</t>
+          <t>187994</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>217445</t>
+          <t>217099</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>152207</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>152207</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>152207</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>167730</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>167730</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>167730</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>152207</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>152207</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>152207</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,72 +2091,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>31356</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22854</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>40600</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>23734</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17035</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>32882</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>17318</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>32299</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,61%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>31356</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>23385</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>40669</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>44370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67514</t>
+          <t>66822</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>268823</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>249151</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>291057</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,59%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>366</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>245899</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>226718</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>266205</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>228609</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>267173</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,39%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,48%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>268823</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>248167</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>290595</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,39%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>484357</t>
+          <t>487417</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>540934</t>
+          <t>543816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -2317,107 +2317,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>399976</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>380089</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>421255</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>57,13%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>54,29%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>60,17%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>580</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>387992</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>367076</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>407764</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>365944</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>406391</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>59,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>55,65%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>61,8%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>1183</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>787968</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>757864</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>815530</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>58,03%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>55,82%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>62,01%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>399976</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>379593</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>421385</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>57,13%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>54,22%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>60,18%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>787968</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>759029</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>816398</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>58,03%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>55,9%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,06%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>700155</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>700155</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>700155</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>983</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>657625</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>657625</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>657625</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>700155</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>700155</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>700155</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11565</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6988</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18056</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>11377</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6775</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17267</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6512</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17131</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>12,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11565</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17987</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31901</t>
+          <t>32799</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29407</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22185</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37111</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>44,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>39341</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>31571</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>47206</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>32883</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>47997</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>43,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>51,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>29407</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>22819</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>36231</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>35,12%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57950</t>
+          <t>58494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79530</t>
+          <t>79433</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -3009,67 +3009,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>42770</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>35100</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50481</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>51,07%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>41,91%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>60,28%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>40768</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>33853</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>49102</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>33376</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>47924</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>44,56%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>37,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>53,67%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42770</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>36028</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>50353</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>51,07%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72587</t>
+          <t>73849</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>95156</t>
+          <t>95605</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -3117,57 +3117,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>83742</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>83742</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>83742</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>91486</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>91486</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>91486</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>83742</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>83742</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>83742</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>58550</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46785</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>70109</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>53749</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>42786</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>65494</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>43132</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>66576</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>12,2%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>58550</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>48016</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>71884</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>96691</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>129267</t>
+          <t>129889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>169123</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154121</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>186480</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>35,9%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>32,71%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>39,58%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>157982</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>141417</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>173596</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>172570</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>35,87%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>32,11%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>169123</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>152941</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>186348</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>35,9%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>301886</t>
+          <t>303634</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>351282</t>
+          <t>350453</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>243481</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>224883</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>259757</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>336</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>228720</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>210942</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>245253</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>213528</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>248069</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,68%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>243481</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>225963</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>261930</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>51,68%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>446293</t>
+          <t>448107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>497933</t>
+          <t>494898</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,29%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>471154</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>471154</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>471154</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>637</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>440451</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>440451</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>440451</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>471154</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>471154</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>471154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12412</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6956</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18474</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11655</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6946</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18110</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7031</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18479</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,33%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12412</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7376</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>19099</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16928</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32574</t>
+          <t>32584</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>66888</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>57315</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>77407</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>40,87%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,02%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>47,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>54438</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>44662</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>65479</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>44872</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>64632</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>34,22%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,08%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>66888</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>56318</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>78392</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>40,87%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107381</t>
+          <t>108208</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135154</t>
+          <t>135985</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>84348</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>73471</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>94126</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>51,54%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>57,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>92986</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>81396</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>102821</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>83122</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>103457</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>58,45%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>51,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>64,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>84348</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>73593</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>95194</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>51,54%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162113</t>
+          <t>162507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>191132</t>
+          <t>191889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,46%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>163649</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>163649</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>163649</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>159079</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>159079</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>159079</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>163649</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>163649</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>163649</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>82527</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>69194</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>98048</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,63%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,65%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>76781</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>63940</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>91413</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>62739</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>90664</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>11,11%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>82527</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>69964</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>98266</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>11,49%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139418</t>
+          <t>141065</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178384</t>
+          <t>182291</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>265418</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>244500</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>286397</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,94%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>361</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>251761</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>231175</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>272647</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>231598</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>273327</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>36,43%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,45%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>39,46%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>265418</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>243762</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>286288</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,94%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>484897</t>
+          <t>485648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>545644</t>
+          <t>544843</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>370600</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>347454</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>392071</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>51,58%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>48,36%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>54,56%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>362475</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>340276</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>383551</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>341036</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>384398</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>52,46%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>55,51%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>533</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>370600</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>346742</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>393469</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>51,58%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>705102</t>
+          <t>704291</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>765422</t>
+          <t>765469</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,31%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>718545</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>718545</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>718545</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>995</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>691016</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>691016</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>691016</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1027</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>718545</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>718545</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>718545</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4833,72 +4833,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1652</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9899</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,43%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6711</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3350</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11871</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3298</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11987</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,43%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4204</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1579</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9352</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>17091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -4946,72 +4946,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>36068</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28623</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42857</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>52,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>41,72%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>62,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>24527</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18839</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30705</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18441</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31091</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>41,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,09%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>52,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>36068</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>28744</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42563</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>52,57%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52370</t>
+          <t>51174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69927</t>
+          <t>70095</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,06%</t>
         </is>
       </c>
     </row>
@@ -5059,72 +5059,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28342</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21885</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35548</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>41,31%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>31,9%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>51,81%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>27465</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>21181</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>33199</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>20993</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>33521</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>46,79%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>36,08%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>56,55%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28342</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21711</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>35649</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>41,31%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47225</t>
+          <t>46691</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64798</t>
+          <t>65539</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,48%</t>
         </is>
       </c>
     </row>
@@ -5172,57 +5172,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>58703</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>58703</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>58703</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5289,72 +5289,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30835</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22790</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41301</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>37459</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28620</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>47709</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>29060</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>47914</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>8,13%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>30835</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>22921</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>39903</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56217</t>
+          <t>56963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>83738</t>
+          <t>82521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -5402,72 +5402,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>188246</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>170568</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>206420</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>39,22%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>35,54%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>43,01%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>159599</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>143991</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>175712</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>144485</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>177687</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>34,62%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>31,23%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>38,12%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>188246</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>171457</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>206159</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>39,22%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>322971</t>
+          <t>324614</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>369882</t>
+          <t>373270</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -5515,72 +5515,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>260849</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>240974</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>278227</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>54,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>57,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>404</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>263936</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>246180</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>280940</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>246569</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>281581</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>57,25%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>60,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>260849</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>243052</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>278044</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>54,35%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>500779</t>
+          <t>500484</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>549357</t>
+          <t>547749</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -5628,57 +5628,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>479930</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>479930</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>479930</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>697</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>460993</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>460993</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>460993</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>479930</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>479930</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>479930</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5745,72 +5745,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11767</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6823</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18090</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10240</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6250</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17785</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>17052</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,06%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11767</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6533</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18029</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15131</t>
+          <t>15351</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30563</t>
+          <t>30738</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -5858,72 +5858,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>71786</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>60770</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>82736</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>39,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>33,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>45,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>52128</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>41999</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>62210</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>42275</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>61787</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>30,83%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>71786</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>61684</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>81853</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>39,28%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109521</t>
+          <t>108571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138685</t>
+          <t>139142</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -5971,72 +5971,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>99219</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>88228</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>110654</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>48,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>60,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>106723</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>96358</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>116892</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>97036</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>117263</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>63,12%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>56,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>69,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>99219</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>88940</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>110207</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>54,29%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>191152</t>
+          <t>190494</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>221882</t>
+          <t>221434</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,93%</t>
         </is>
       </c>
     </row>
@@ -6084,57 +6084,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>182772</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>182772</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>182772</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>169091</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>169091</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>169091</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>182772</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>182772</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>182772</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6201,72 +6201,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>46806</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35473</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>59188</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>54410</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>43271</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>66941</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>42890</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>66533</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,9%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>46806</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>36415</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>59307</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84935</t>
+          <t>85750</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119197</t>
+          <t>119731</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -6314,107 +6314,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>296100</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>273994</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>318296</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,49%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>37,47%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>43,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>350</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>236252</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>215264</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>257335</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>216586</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>257464</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,3%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,25%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>296100</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>274204</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>318609</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>40,49%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>37,38%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>532353</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>503277</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>562983</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>37,49%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>43,57%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>532353</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>501213</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>563957</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>37,49%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -6427,72 +6427,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>388410</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>363706</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>409169</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>53,11%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>49,73%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>55,95%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>609</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>398124</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>376837</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>419647</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>374871</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>420147</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>57,8%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>54,71%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>60,93%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>388410</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>365435</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>411218</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>53,11%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>753530</t>
+          <t>754820</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>818227</t>
+          <t>813477</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>
@@ -6540,57 +6540,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>731316</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>731316</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>731316</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1038</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>688786</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>688786</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>688786</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1046</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>731316</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>731316</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>731316</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6888,72 +6888,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9511</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5440</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15636</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,59%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4430</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1810</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8928</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17092</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>14113</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>8636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>21175</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -7001,72 +7001,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25211</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18924</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32034</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>33,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>24861</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16631</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34735</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>45,47%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27782</t>
+          <t>21872</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35195</t>
+          <t>28518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>52643</t>
+          <t>47083</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41898</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>56491</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>54,59%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25387</t>
+          <t>22010</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16381</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33880</t>
+          <t>28412</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24077</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30997</t>
+          <t>25790</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>49464</t>
+          <t>42294</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>33401</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60649</t>
+          <t>50660</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -7227,57 +7227,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7344,72 +7344,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38318</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24678</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>62514</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>13,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>21545</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14420</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31605</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42777</t>
+          <t>19404</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27646</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75957</t>
+          <t>26942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>64323</t>
+          <t>57722</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49313</t>
+          <t>44727</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101856</t>
+          <t>87282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -7457,72 +7457,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>242025</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>220351</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>263584</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>51,2%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>46,62%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>55,76%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>234318</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>212490</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>277575</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>51,39%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>46,6%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>60,87%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>217266</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>225379</t>
+          <t>197380</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>275019</t>
+          <t>234068</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>485224</t>
+          <t>459291</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>452206</t>
+          <t>430302</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>531664</t>
+          <t>487814</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>192341</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>173677</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>214268</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40,69%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>45,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>200137</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>162944</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>221177</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>43,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>35,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>48,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>219651</t>
+          <t>191436</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>194585</t>
+          <t>175065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>245916</t>
+          <t>211496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>419788</t>
+          <t>383777</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>372495</t>
+          <t>354775</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>451313</t>
+          <t>411560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>45,69%</t>
         </is>
       </c>
     </row>
@@ -7683,57 +7683,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>472684</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>472684</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>472684</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>637</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>456000</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>456000</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>456000</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>513334</t>
+          <t>428106</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>513334</t>
+          <t>428106</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>513334</t>
+          <t>428106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>969334</t>
+          <t>900789</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>969334</t>
+          <t>900789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>969334</t>
+          <t>900789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7800,72 +7800,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15188</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10131</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22991</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,03%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>8977</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5088</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14557</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17462</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25852</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>26439</t>
+          <t>24282</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18954</t>
+          <t>16522</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36807</t>
+          <t>32802</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -7913,72 +7913,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>75544</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>63228</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>86946</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>46,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>38,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>53,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>62025</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>52244</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>72692</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>41,81%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49,01%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>78284</t>
+          <t>63121</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65742</t>
+          <t>53394</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91721</t>
+          <t>73053</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>140310</t>
+          <t>138665</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123333</t>
+          <t>123334</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155463</t>
+          <t>153314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>49,03%</t>
         </is>
       </c>
     </row>
@@ -8026,72 +8026,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>73188</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>62070</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>85235</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>44,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>37,87%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>52,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>77332</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>66656</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>88311</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>52,13%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>44,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>59,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>83117</t>
+          <t>76560</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69972</t>
+          <t>65809</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95964</t>
+          <t>86223</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>160449</t>
+          <t>149748</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144645</t>
+          <t>135386</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176715</t>
+          <t>165678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -8139,57 +8139,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>163920</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>163920</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>163920</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>148333</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>148333</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>148333</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>178864</t>
+          <t>148775</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>178864</t>
+          <t>148775</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>178864</t>
+          <t>148775</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>327198</t>
+          <t>312695</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>327198</t>
+          <t>312695</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>327198</t>
+          <t>312695</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8256,72 +8256,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>63017</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>47109</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>92568</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>34952</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>24725</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>45418</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>70385</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53880</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105692</t>
+          <t>42514</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>105337</t>
+          <t>96117</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86001</t>
+          <t>79038</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140210</t>
+          <t>124663</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -8369,72 +8369,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>342781</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>315951</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>367406</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>49,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>45,57%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>52,99%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>428</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>321204</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>294060</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>365101</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>48,74%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>44,62%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>55,4%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>356973</t>
+          <t>302259</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>328441</t>
+          <t>282274</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>383839</t>
+          <t>324162</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>678176</t>
+          <t>645039</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>638780</t>
+          <t>609595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>735746</t>
+          <t>679740</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,61%</t>
         </is>
       </c>
     </row>
@@ -8482,72 +8482,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>287538</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>264018</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>311669</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>41,47%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>38,08%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>44,95%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>454</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>302855</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>262799</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>330240</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>45,96%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>39,88%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>50,11%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>326845</t>
+          <t>288281</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>298174</t>
+          <t>267239</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>353095</t>
+          <t>308643</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>629700</t>
+          <t>575818</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>582165</t>
+          <t>543448</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>667192</t>
+          <t>610665</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -8595,57 +8595,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>693336</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>693336</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>693336</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>934</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>659011</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>659011</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>659011</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>754203</t>
+          <t>623639</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>754203</t>
+          <t>623639</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>754203</t>
+          <t>623639</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1413213</t>
+          <t>1316974</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1413213</t>
+          <t>1316974</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1413213</t>
+          <t>1316974</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
